--- a/artfynd/A 17766-2024 artfynd.xlsx
+++ b/artfynd/A 17766-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AZ46"/>
+  <dimension ref="A1:AZ48"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -5143,10 +5143,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>103581468</v>
+        <v>137402371</v>
       </c>
       <c r="B40" t="n">
-        <v>45044</v>
+        <v>43358</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -5154,21 +5154,21 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>102018</v>
+        <v>101260</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Bredbrämad bastardsvärmare</t>
+          <t>Svartfläckig blåvinge</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Zygaena lonicerae</t>
+          <t>Phengaris arion</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Scheven, 1777)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I40" t="inlineStr">
@@ -5177,11 +5177,7 @@
         </is>
       </c>
       <c r="J40" t="inlineStr"/>
-      <c r="K40" t="inlineStr">
-        <is>
-          <t>imago/adult</t>
-        </is>
-      </c>
+      <c r="K40" t="inlineStr"/>
       <c r="L40" t="inlineStr"/>
       <c r="M40" t="inlineStr"/>
       <c r="N40" t="inlineStr"/>
@@ -5191,10 +5187,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>701184</v>
+        <v>701234</v>
       </c>
       <c r="R40" t="n">
-        <v>6391360</v>
+        <v>6391394</v>
       </c>
       <c r="S40" t="n">
         <v>1</v>
@@ -5221,12 +5217,12 @@
       </c>
       <c r="Y40" t="inlineStr">
         <is>
-          <t>2022-07-09</t>
+          <t>2026-07-15</t>
         </is>
       </c>
       <c r="AA40" t="inlineStr">
         <is>
-          <t>2022-07-09</t>
+          <t>2026-07-15</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -5250,19 +5246,23 @@
           <t>Arne Pettersson</t>
         </is>
       </c>
-      <c r="AY40" t="inlineStr"/>
+      <c r="AY40" t="inlineStr">
+        <is>
+          <t>Biogeografisk uppföljning av fjärilar</t>
+        </is>
+      </c>
       <c r="AZ40" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/103581468</t>
+          <t>https://artportalen.se/Sighting/137402371</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>118098657</v>
+        <v>137402384</v>
       </c>
       <c r="B41" t="n">
-        <v>45044</v>
+        <v>43358</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -5270,54 +5270,46 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>102018</v>
+        <v>101260</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Bredbrämad bastardsvärmare</t>
+          <t>Svartfläckig blåvinge</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Zygaena lonicerae</t>
+          <t>Phengaris arion</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Scheven, 1777)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I41" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J41" t="inlineStr"/>
-      <c r="K41" t="inlineStr">
-        <is>
-          <t>imago/adult</t>
-        </is>
-      </c>
+      <c r="K41" t="inlineStr"/>
       <c r="L41" t="inlineStr"/>
-      <c r="M41" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
+      <c r="M41" t="inlineStr"/>
       <c r="N41" t="inlineStr"/>
       <c r="P41" t="inlineStr">
         <is>
-          <t>Stadshajden, Gtl</t>
+          <t>Ölbäck, Gtl</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>701186</v>
+        <v>701239</v>
       </c>
       <c r="R41" t="n">
-        <v>6391366</v>
+        <v>6391401</v>
       </c>
       <c r="S41" t="n">
-        <v>11</v>
+        <v>1</v>
       </c>
       <c r="T41" t="inlineStr">
         <is>
@@ -5341,22 +5333,12 @@
       </c>
       <c r="Y41" t="inlineStr">
         <is>
-          <t>2024-06-29</t>
-        </is>
-      </c>
-      <c r="Z41" t="inlineStr">
-        <is>
-          <t>11:55</t>
+          <t>2026-07-15</t>
         </is>
       </c>
       <c r="AA41" t="inlineStr">
         <is>
-          <t>2024-06-29</t>
-        </is>
-      </c>
-      <c r="AB41" t="inlineStr">
-        <is>
-          <t>12:01</t>
+          <t>2026-07-15</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -5365,33 +5347,38 @@
       <c r="AE41" t="b">
         <v>0</v>
       </c>
+      <c r="AF41" t="inlineStr"/>
       <c r="AG41" t="b">
         <v>0</v>
       </c>
       <c r="AT41" t="inlineStr"/>
       <c r="AW41" t="inlineStr">
         <is>
-          <t>Peter Olofsson</t>
+          <t>Arne Pettersson</t>
         </is>
       </c>
       <c r="AX41" t="inlineStr">
         <is>
-          <t>Peter Olofsson, Evelina Lindgren</t>
-        </is>
-      </c>
-      <c r="AY41" t="inlineStr"/>
+          <t>Arne Pettersson</t>
+        </is>
+      </c>
+      <c r="AY41" t="inlineStr">
+        <is>
+          <t>Biogeografisk uppföljning av fjärilar</t>
+        </is>
+      </c>
       <c r="AZ41" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/118098657</t>
+          <t>https://artportalen.se/Sighting/137402384</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>135246965</v>
+        <v>103581468</v>
       </c>
       <c r="B42" t="n">
-        <v>45055</v>
+        <v>45044</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5428,25 +5415,21 @@
         </is>
       </c>
       <c r="L42" t="inlineStr"/>
-      <c r="M42" t="inlineStr">
-        <is>
-          <t>friflygande</t>
-        </is>
-      </c>
+      <c r="M42" t="inlineStr"/>
       <c r="N42" t="inlineStr"/>
       <c r="P42" t="inlineStr">
         <is>
-          <t>Stadshajden, Gtl</t>
+          <t>Ölbäck, Gtl</t>
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>701159</v>
+        <v>701184</v>
       </c>
       <c r="R42" t="n">
-        <v>6391419</v>
+        <v>6391360</v>
       </c>
       <c r="S42" t="n">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="T42" t="inlineStr">
         <is>
@@ -5470,22 +5453,12 @@
       </c>
       <c r="Y42" t="inlineStr">
         <is>
-          <t>2026-07-19</t>
-        </is>
-      </c>
-      <c r="Z42" t="inlineStr">
-        <is>
-          <t>11:45</t>
+          <t>2022-07-09</t>
         </is>
       </c>
       <c r="AA42" t="inlineStr">
         <is>
-          <t>2026-07-19</t>
-        </is>
-      </c>
-      <c r="AB42" t="inlineStr">
-        <is>
-          <t>11:46</t>
+          <t>2022-07-09</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -5494,71 +5467,89 @@
       <c r="AE42" t="b">
         <v>0</v>
       </c>
+      <c r="AF42" t="inlineStr"/>
       <c r="AG42" t="b">
         <v>0</v>
       </c>
       <c r="AT42" t="inlineStr"/>
       <c r="AW42" t="inlineStr">
         <is>
-          <t>Edvin Klein</t>
+          <t>Arne Pettersson</t>
         </is>
       </c>
       <c r="AX42" t="inlineStr">
         <is>
-          <t>Edvin Klein, Musse Björklund</t>
+          <t>Arne Pettersson</t>
         </is>
       </c>
       <c r="AY42" t="inlineStr"/>
       <c r="AZ42" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135246965</t>
+          <t>https://artportalen.se/Sighting/103581468</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>61244250</v>
+        <v>118098657</v>
       </c>
       <c r="B43" t="n">
-        <v>102225</v>
+        <v>45044</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>221223</v>
+        <v>102018</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Vippärt</t>
+          <t>Bredbrämad bastardsvärmare</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Lathyrus niger</t>
+          <t>Zygaena lonicerae</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(L.) Bernh.</t>
-        </is>
-      </c>
-      <c r="I43" t="inlineStr"/>
+          <t>(Scheven, 1777)</t>
+        </is>
+      </c>
+      <c r="I43" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="J43" t="inlineStr"/>
+      <c r="K43" t="inlineStr">
+        <is>
+          <t>imago/adult</t>
+        </is>
+      </c>
+      <c r="L43" t="inlineStr"/>
+      <c r="M43" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
+      <c r="N43" t="inlineStr"/>
       <c r="P43" t="inlineStr">
         <is>
-          <t>Ölbäcks naturreservat, Gtl</t>
+          <t>Stadshajden, Gtl</t>
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>701253</v>
+        <v>701186</v>
       </c>
       <c r="R43" t="n">
-        <v>6391419</v>
+        <v>6391366</v>
       </c>
       <c r="S43" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="T43" t="inlineStr">
         <is>
@@ -5582,12 +5573,22 @@
       </c>
       <c r="Y43" t="inlineStr">
         <is>
-          <t>2016-08-22</t>
+          <t>2024-06-29</t>
+        </is>
+      </c>
+      <c r="Z43" t="inlineStr">
+        <is>
+          <t>11:55</t>
         </is>
       </c>
       <c r="AA43" t="inlineStr">
         <is>
-          <t>2016-08-22</t>
+          <t>2024-06-29</t>
+        </is>
+      </c>
+      <c r="AB43" t="inlineStr">
+        <is>
+          <t>12:01</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -5602,65 +5603,82 @@
       <c r="AT43" t="inlineStr"/>
       <c r="AW43" t="inlineStr">
         <is>
-          <t>Elin Götmark</t>
+          <t>Peter Olofsson</t>
         </is>
       </c>
       <c r="AX43" t="inlineStr">
         <is>
-          <t>Elin Götmark, Linnea Helmersson</t>
+          <t>Peter Olofsson, Evelina Lindgren</t>
         </is>
       </c>
       <c r="AY43" t="inlineStr"/>
       <c r="AZ43" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/61244250</t>
+          <t>https://artportalen.se/Sighting/118098657</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>106605049</v>
+        <v>135246965</v>
       </c>
       <c r="B44" t="n">
-        <v>102225</v>
+        <v>45055</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>221223</v>
+        <v>102018</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Vippärt</t>
+          <t>Bredbrämad bastardsvärmare</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Lathyrus niger</t>
+          <t>Zygaena lonicerae</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(L.) Bernh.</t>
-        </is>
-      </c>
-      <c r="I44" t="inlineStr"/>
+          <t>(Scheven, 1777)</t>
+        </is>
+      </c>
+      <c r="I44" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J44" t="inlineStr"/>
+      <c r="K44" t="inlineStr">
+        <is>
+          <t>imago/adult</t>
+        </is>
+      </c>
+      <c r="L44" t="inlineStr"/>
+      <c r="M44" t="inlineStr">
+        <is>
+          <t>friflygande</t>
+        </is>
+      </c>
+      <c r="N44" t="inlineStr"/>
       <c r="P44" t="inlineStr">
         <is>
-          <t>Ölbäck, ca 400 m SSV P-plats, Gtl</t>
+          <t>Stadshajden, Gtl</t>
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>701100</v>
+        <v>701159</v>
       </c>
       <c r="R44" t="n">
-        <v>6391270</v>
+        <v>6391419</v>
       </c>
       <c r="S44" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="T44" t="inlineStr">
         <is>
@@ -5684,12 +5702,22 @@
       </c>
       <c r="Y44" t="inlineStr">
         <is>
-          <t>1988-01-01</t>
+          <t>2026-07-19</t>
+        </is>
+      </c>
+      <c r="Z44" t="inlineStr">
+        <is>
+          <t>11:45</t>
         </is>
       </c>
       <c r="AA44" t="inlineStr">
         <is>
-          <t>1992-12-31</t>
+          <t>2026-07-19</t>
+        </is>
+      </c>
+      <c r="AB44" t="inlineStr">
+        <is>
+          <t>11:46</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5704,66 +5732,62 @@
       <c r="AT44" t="inlineStr"/>
       <c r="AW44" t="inlineStr">
         <is>
-          <t>Jörgen Petersson</t>
+          <t>Edvin Klein</t>
         </is>
       </c>
       <c r="AX44" t="inlineStr">
         <is>
-          <t>Torgny Rosvall</t>
-        </is>
-      </c>
-      <c r="AY44" t="inlineStr">
-        <is>
-          <t>Projekt Gotlands Flora</t>
-        </is>
-      </c>
+          <t>Edvin Klein, Musse Björklund</t>
+        </is>
+      </c>
+      <c r="AY44" t="inlineStr"/>
       <c r="AZ44" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/106605049</t>
+          <t>https://artportalen.se/Sighting/135246965</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>120661712</v>
+        <v>61244250</v>
       </c>
       <c r="B45" t="n">
-        <v>90665</v>
+        <v>102225</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>245042</v>
+        <v>221223</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Besk kastanjemusseron</t>
+          <t>Vippärt</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Tricholoma batschii</t>
+          <t>Lathyrus niger</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>Mort. Chr. &amp; Noordel.</t>
+          <t>(L.) Bernh.</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
       <c r="P45" t="inlineStr">
         <is>
-          <t>Stadshajden, Stadshajden, Gtl</t>
+          <t>Ölbäcks naturreservat, Gtl</t>
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>701227</v>
+        <v>701253</v>
       </c>
       <c r="R45" t="n">
-        <v>6391428</v>
+        <v>6391419</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5790,12 +5814,12 @@
       </c>
       <c r="Y45" t="inlineStr">
         <is>
-          <t>2024-10-25</t>
+          <t>2016-08-22</t>
         </is>
       </c>
       <c r="AA45" t="inlineStr">
         <is>
-          <t>2024-10-25</t>
+          <t>2016-08-22</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5810,62 +5834,62 @@
       <c r="AT45" t="inlineStr"/>
       <c r="AW45" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Elin Götmark</t>
         </is>
       </c>
       <c r="AX45" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Elin Götmark, Linnea Helmersson</t>
         </is>
       </c>
       <c r="AY45" t="inlineStr"/>
       <c r="AZ45" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/120661712</t>
+          <t>https://artportalen.se/Sighting/61244250</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>120661706</v>
+        <v>106605049</v>
       </c>
       <c r="B46" t="n">
-        <v>87262</v>
+        <v>102225</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>248956</v>
+        <v>221223</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Gulsträngad fagerspindling</t>
+          <t>Vippärt</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Cortinarius haasii</t>
+          <t>Lathyrus niger</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(M.M.Moser) M.M.Moser</t>
+          <t>(L.) Bernh.</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
       <c r="P46" t="inlineStr">
         <is>
-          <t>Stadshajden, Stadshajden, Gtl</t>
+          <t>Ölbäck, ca 400 m SSV P-plats, Gtl</t>
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>701191</v>
+        <v>701100</v>
       </c>
       <c r="R46" t="n">
-        <v>6391369</v>
+        <v>6391270</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5892,12 +5916,12 @@
       </c>
       <c r="Y46" t="inlineStr">
         <is>
-          <t>2024-10-25</t>
+          <t>1988-01-01</t>
         </is>
       </c>
       <c r="AA46" t="inlineStr">
         <is>
-          <t>2024-10-25</t>
+          <t>1992-12-31</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -5912,16 +5936,224 @@
       <c r="AT46" t="inlineStr"/>
       <c r="AW46" t="inlineStr">
         <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AX46" t="inlineStr">
+        <is>
+          <t>Torgny Rosvall</t>
+        </is>
+      </c>
+      <c r="AY46" t="inlineStr">
+        <is>
+          <t>Projekt Gotlands Flora</t>
+        </is>
+      </c>
+      <c r="AZ46" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/106605049</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="n">
+        <v>120661712</v>
+      </c>
+      <c r="B47" t="n">
+        <v>90665</v>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E47" t="n">
+        <v>245042</v>
+      </c>
+      <c r="F47" t="inlineStr">
+        <is>
+          <t>Besk kastanjemusseron</t>
+        </is>
+      </c>
+      <c r="G47" t="inlineStr">
+        <is>
+          <t>Tricholoma batschii</t>
+        </is>
+      </c>
+      <c r="H47" t="inlineStr">
+        <is>
+          <t>Mort. Chr. &amp; Noordel.</t>
+        </is>
+      </c>
+      <c r="I47" t="inlineStr"/>
+      <c r="P47" t="inlineStr">
+        <is>
+          <t>Stadshajden, Stadshajden, Gtl</t>
+        </is>
+      </c>
+      <c r="Q47" t="n">
+        <v>701227</v>
+      </c>
+      <c r="R47" t="n">
+        <v>6391428</v>
+      </c>
+      <c r="S47" t="n">
+        <v>10</v>
+      </c>
+      <c r="T47" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U47" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V47" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W47" t="inlineStr">
+        <is>
+          <t>Endre</t>
+        </is>
+      </c>
+      <c r="Y47" t="inlineStr">
+        <is>
+          <t>2024-10-25</t>
+        </is>
+      </c>
+      <c r="AA47" t="inlineStr">
+        <is>
+          <t>2024-10-25</t>
+        </is>
+      </c>
+      <c r="AD47" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE47" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG47" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT47" t="inlineStr"/>
+      <c r="AW47" t="inlineStr">
+        <is>
           <t>Liam Sebestyén</t>
         </is>
       </c>
-      <c r="AX46" t="inlineStr">
+      <c r="AX47" t="inlineStr">
         <is>
           <t>Liam Sebestyén</t>
         </is>
       </c>
-      <c r="AY46" t="inlineStr"/>
-      <c r="AZ46" t="inlineStr">
+      <c r="AY47" t="inlineStr"/>
+      <c r="AZ47" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120661712</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="n">
+        <v>120661706</v>
+      </c>
+      <c r="B48" t="n">
+        <v>87262</v>
+      </c>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E48" t="n">
+        <v>248956</v>
+      </c>
+      <c r="F48" t="inlineStr">
+        <is>
+          <t>Gulsträngad fagerspindling</t>
+        </is>
+      </c>
+      <c r="G48" t="inlineStr">
+        <is>
+          <t>Cortinarius haasii</t>
+        </is>
+      </c>
+      <c r="H48" t="inlineStr">
+        <is>
+          <t>(M.M.Moser) M.M.Moser</t>
+        </is>
+      </c>
+      <c r="I48" t="inlineStr"/>
+      <c r="P48" t="inlineStr">
+        <is>
+          <t>Stadshajden, Stadshajden, Gtl</t>
+        </is>
+      </c>
+      <c r="Q48" t="n">
+        <v>701191</v>
+      </c>
+      <c r="R48" t="n">
+        <v>6391369</v>
+      </c>
+      <c r="S48" t="n">
+        <v>10</v>
+      </c>
+      <c r="T48" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U48" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V48" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W48" t="inlineStr">
+        <is>
+          <t>Endre</t>
+        </is>
+      </c>
+      <c r="Y48" t="inlineStr">
+        <is>
+          <t>2024-10-25</t>
+        </is>
+      </c>
+      <c r="AA48" t="inlineStr">
+        <is>
+          <t>2024-10-25</t>
+        </is>
+      </c>
+      <c r="AD48" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE48" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG48" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT48" t="inlineStr"/>
+      <c r="AW48" t="inlineStr">
+        <is>
+          <t>Liam Sebestyén</t>
+        </is>
+      </c>
+      <c r="AX48" t="inlineStr">
+        <is>
+          <t>Liam Sebestyén</t>
+        </is>
+      </c>
+      <c r="AY48" t="inlineStr"/>
+      <c r="AZ48" t="inlineStr">
         <is>
           <t>https://artportalen.se/Sighting/120661706</t>
         </is>
@@ -5974,6 +6206,8 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ44" r:id="rId43"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ45" r:id="rId44"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ46" r:id="rId45"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ47" r:id="rId46"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ48" r:id="rId47"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
